--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N108_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N108_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.79238573064767</v>
+        <v>10.36626268123025</v>
       </c>
       <c r="D2" t="n">
-        <v>64.53354801033895</v>
+        <v>10.48670155168008</v>
       </c>
       <c r="E2" t="n">
-        <v>13.74856577452069</v>
+        <v>2.234141938359612</v>
       </c>
       <c r="F2" t="n">
-        <v>21.45326312351912</v>
+        <v>3.486155257571858</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>68.68978411370277</v>
+        <v>11.1620899184767</v>
       </c>
       <c r="D3" t="n">
-        <v>67.9910429937192</v>
+        <v>11.04854448647937</v>
       </c>
       <c r="E3" t="n">
-        <v>13.74856577452069</v>
+        <v>2.234141938359612</v>
       </c>
       <c r="F3" t="n">
-        <v>21.45326312351912</v>
+        <v>3.486155257571858</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.37350445684752</v>
+        <v>4.773194474237722</v>
       </c>
       <c r="D4" t="n">
-        <v>27.73497010178761</v>
+        <v>4.506932641540487</v>
       </c>
       <c r="E4" t="n">
-        <v>13.74856577452069</v>
+        <v>2.234141938359612</v>
       </c>
       <c r="F4" t="n">
-        <v>21.45326312351912</v>
+        <v>3.486155257571858</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>70.17244793648432</v>
+        <v>11.4030227896787</v>
       </c>
       <c r="D5" t="n">
-        <v>70.10104757029028</v>
+        <v>11.39142023017217</v>
       </c>
       <c r="E5" t="n">
-        <v>13.74856577452069</v>
+        <v>2.234141938359612</v>
       </c>
       <c r="F5" t="n">
-        <v>21.45326312351912</v>
+        <v>3.486155257571858</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>57.33022612675423</v>
+        <v>9.316161745597562</v>
       </c>
       <c r="D6" t="n">
-        <v>55.70566204143586</v>
+        <v>9.052170081733328</v>
       </c>
       <c r="E6" t="n">
-        <v>13.74856577452069</v>
+        <v>2.234141938359612</v>
       </c>
       <c r="F6" t="n">
-        <v>21.45326312351912</v>
+        <v>3.486155257571858</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>62.55835192311906</v>
+        <v>10.16573218750685</v>
       </c>
       <c r="D7" t="n">
-        <v>14.02477965760762</v>
+        <v>2.279026694361238</v>
       </c>
       <c r="E7" t="n">
-        <v>13.74856577452069</v>
+        <v>2.234141938359612</v>
       </c>
       <c r="F7" t="n">
-        <v>21.45326312351912</v>
+        <v>3.486155257571858</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
